--- a/ksoft_old/docs/fields_details/jalmeida/CE0302(2).xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/CE0302(2).xlsx
@@ -9869,13 +9869,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37657130-A6DE-41BC-9960-644EEDAD634B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E127AA03-23CE-45E8-BD43-83703D6531F9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EF574C0-C000-4B9E-AF00-B36474DDC41B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8A074C8-1AB4-408A-8C36-5F7485D10015}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AADDBEE-46AF-4C03-AC50-362EB5F4520A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A1386C2-DD95-4ED1-9561-E8FCB59C2F2B}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/CE0302(2).xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/CE0302(2).xlsx
@@ -9869,13 +9869,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E127AA03-23CE-45E8-BD43-83703D6531F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A60FA5D-138A-4DCA-AB39-FFCE3BD75B10}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8A074C8-1AB4-408A-8C36-5F7485D10015}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B0A8637-0736-4490-9C77-210D670D0BAE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A1386C2-DD95-4ED1-9561-E8FCB59C2F2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{936268C5-16B7-42EC-AD26-616B59547257}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/CE0302(2).xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/CE0302(2).xlsx
@@ -9869,13 +9869,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A60FA5D-138A-4DCA-AB39-FFCE3BD75B10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37657130-A6DE-41BC-9960-644EEDAD634B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B0A8637-0736-4490-9C77-210D670D0BAE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EF574C0-C000-4B9E-AF00-B36474DDC41B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{936268C5-16B7-42EC-AD26-616B59547257}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AADDBEE-46AF-4C03-AC50-362EB5F4520A}"/>
 </file>